--- a/results/Int All Data -0.2/Linea_fi_all.xlsx
+++ b/results/Int All Data -0.2/Linea_fi_all.xlsx
@@ -1706,7 +1706,7 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>0.008752327746741173 +/- 0.002733338157207217</t>
+          <t>0.00878336436995657 +/- 0.0027482750226273146</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
@@ -2346,72 +2346,72 @@
       </c>
       <c r="BW3" t="inlineStr">
         <is>
+          <t>-0.0005331556147950778 +/- 0.0004987214110995013</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.008430523158947 +/- 0.0016327890703098724</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.0030656447850716086 +/- 0.0011996001332888898</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.0030656447850716086 +/- 0.0011996001332888898</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.004065311562812346 +/- 0.003928067185149314</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>-0.0028657114295235096 +/- 0.0016807091253473374</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.005864711762745722 +/- 0.0019095699809256093</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>-0.0025991336221260044 +/- 0.001992657965708234</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>-0.0007664111962679243 +/- 0.0005970167566534233</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>-0.0017327557480840028 +/- 0.0012450211057827216</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>0.3121626124625124 +/- 0.005949300608189757</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>0.011296234588470488 +/- 0.0024687699356203243</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>0.24258580473175603 +/- 0.007142158764832265</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
           <t>-0.0005664778407197702 +/- 0.0005173000565231689</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.008430523158947 +/- 0.0016327890703098724</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.0030656447850716086 +/- 0.0011996001332888898</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.0030656447850716086 +/- 0.0011996001332888898</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.004065311562812346 +/- 0.003928067185149314</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>-0.0028657114295235096 +/- 0.0016807091253473374</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.005864711762745722 +/- 0.0019095699809256093</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>-0.0025991336221260044 +/- 0.001992657965708234</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>-0.0007664111962679243 +/- 0.0005970167566534233</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>-0.0017327557480840028 +/- 0.0012450211057827216</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>0.3121626124625124 +/- 0.005949300608189757</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
-        <is>
-          <t>0.011296234588470488 +/- 0.0024687699356203243</t>
-        </is>
-      </c>
-      <c r="CI3" t="inlineStr">
-        <is>
-          <t>0.24258580473175603 +/- 0.007142158764832265</t>
-        </is>
-      </c>
-      <c r="CJ3" t="inlineStr">
-        <is>
-          <t>-0.0005331556147950778 +/- 0.0004987214110995013</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>-0.021754498714653014 +/- 0.0017067187307055881</t>
+          <t>-0.021786632390745554 +/- 0.0017588601778154112</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.04787917737789198 +/- 0.003914509597131363</t>
+          <t>0.04791131105398453 +/- 0.0038839234017773254</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.014657666345226639 +/- 0.0015021949785339645</t>
+          <t>0.014721954355512712 +/- 0.0015267556524638881</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -3786,74 +3786,74 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
+          <t>0.019672131147540982 +/- 0.002116628432421002</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.030536804885888814 +/- 0.0038866342655588236</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-0.0005464480874316946 +/- 0.0006107360977177684</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.0005143040822886746 +/- 0.00038572806171650604</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.011636129861780786 +/- 0.0015668347935652754</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>-0.006171648987463818 +/- 0.0017417186993435227</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.003278688524590201 +/- 0.0011482205785594128</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.03162970106075218 +/- 0.0029954349745346643</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.09697846351655418 +/- 0.00521496239976108</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.022661523625843793 +/- 0.0025401900482327636</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.17033108325297336 +/- 0.00612501466549107</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>-0.0026358084217293467 +/- 0.0007714561234329703</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.02864030858244939 +/- 0.002449913084190456</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>0.019639987142397942 +/- 0.0021002116649205585</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>0.030536804885888814 +/- 0.0038866342655588236</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-0.0005464480874316946 +/- 0.0006107360977177684</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0.0005143040822886746 +/- 0.00038572806171650604</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0.011636129861780786 +/- 0.0015668347935652754</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>-0.006171648987463818 +/- 0.0017417186993435227</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>0.003278688524590201 +/- 0.0011482205785594128</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>0.03162970106075218 +/- 0.0029954349745346643</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>0.09697846351655418 +/- 0.00521496239976108</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>0.022661523625843793 +/- 0.0025401900482327636</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>0.17033108325297336 +/- 0.00612501466549107</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>-0.0026358084217293467 +/- 0.0007714561234329703</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.02864030858244939 +/- 0.002449913084190456</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>0.019672131147540982 +/- 0.002116628432421002</t>
-        </is>
-      </c>
       <c r="BO5" t="inlineStr">
         <is>
           <t>0.03368691738990679 +/- 0.003915240110211536</t>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>0.11327547412407586 +/- 0.0026200815007797916</t>
+          <t>0.11324333011893281 +/- 0.002571721303628363</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>0.028704596592735453 +/- 0.0025434420131402696</t>
+          <t>0.028736740597878497 +/- 0.002507232401157195</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>-0.0017504774029281078 +/- 0.0010089667399202857</t>
+          <t>-0.0017186505410566877 +/- 0.001057495081211744</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>-0.008561425843411874 +/- 0.0016626299028146246</t>
+          <t>-0.008529598981540454 +/- 0.0016216090646539647</t>
         </is>
       </c>
       <c r="DL6" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.00022421524663679415 +/- 0.00032190504872264033</t>
+          <t>0.0002562459961563346 +/- 0.0003449817301175206</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="ET8" t="inlineStr">
         <is>
-          <t>-0.00409993593850092 +/- 0.0008077847670031065</t>
+          <t>-0.00406790518898138 +/- 0.0008235080161551857</t>
         </is>
       </c>
       <c r="EU8" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.002018474170372886 +/- 0.0010427472223146106</t>
+          <t>-0.0020526855969893788 +/- 0.0010032759697992076</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.009887102292165606 +/- 0.001556149902913998</t>
+          <t>0.009750256585699646 +/- 0.0015844729629708291</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.0019842627437564155 +/- 0.0014579046016190704</t>
+          <t>-0.0020526855969893788 +/- 0.0014990696065827632</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0015737256243585685 +/- 0.0014122317783476152</t>
+          <t>0.0016763599042080135 +/- 0.0014143021969616363</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-0.003489565514881976 +/- 0.0011117397748389944</t>
+          <t>-0.0032500855285665263 +/- 0.0007377303678702544</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-0.0028053369825521536 +/- 0.0021133691702333846</t>
+          <t>-0.00273691412931919 +/- 0.002141974114608072</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.0019842627437564484 +/- 0.00133205079260565</t>
+          <t>0.001881628463906937 +/- 0.0013534068043005297</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.0019842627437564155 +/- 0.0014579046016190704</t>
+          <t>-0.0018474170372904442 +/- 0.0014849493270072374</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.000855285665412242 +/- 0.0011059343055247618</t>
+          <t>-0.0007526513855627748 +/- 0.0013667454228832217</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-0.0005473828258638292 +/- 0.0007831353501375005</t>
+          <t>-0.0008210742387957492 +/- 0.0007979407314191544</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>3.421142661650389e-05 +/- 0.0010867177676543685</t>
+          <t>0.0003421142661649168 +/- 0.0008921248587345425</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.017892576120424254 +/- 0.001467905436395826</t>
+          <t>0.01809784468012319 +/- 0.001159661392862009</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.016421484775915186 +/- 0.0023947998631542876</t>
+          <t>0.015771467670201843 +/- 0.0024212893984564545</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.0005815942524803553 +/- 0.00030790283954840305</t>
+          <t>0.0017105713308245064 +/- 0.0006491161806709093</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.0004447485460143952 +/- 0.00030790283954841417</t>
+          <t>0.000478959972630888 +/- 0.0002736914129319201</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.0004789599726308325 +/- 0.000438120029930392</t>
+          <t>-0.0005131713992473253 +/- 0.0004653257101859445</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -6881,17 +6881,17 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0004447485460143952 +/- 0.00030790283954841417</t>
+          <t>0.0005473828258638735 +/- 0.00027369141293192293</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.003900102634279856 +/- 0.0014849493270072162</t>
+          <t>0.0038658912076633524 +/- 0.001491633893711356</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.005610673965104363 +/- 0.001732328279325651</t>
+          <t>0.005473828258638414 +/- 0.0015826251804612302</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>0.004926445432774551 +/- 0.0013786822907704197</t>
+          <t>0.005234348272322964 +/- 0.0015755838439506435</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0.003900102634279856 +/- 0.0014849493270072162</t>
+          <t>0.0038658912076633633 +/- 0.0014837665714814367</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.004892234006158069 +/- 0.0006850832841088315</t>
+          <t>0.004481696886760178 +/- 0.0005398472062285143</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>0.01542935340403694 +/- 0.0017136475930712633</t>
+          <t>0.018713650359219968 +/- 0.0017514780343715556</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -7001,17 +7001,17 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>-0.013924050632911366 +/- 0.0011454443409362365</t>
+          <t>-0.009237085186452254 +/- 0.000733753355782662</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>-0.002839548409168657 +/- 0.0015149907509739583</t>
+          <t>-0.002907971262401643 +/- 0.0015165350844544231</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-0.002839548409168657 +/- 0.0015149907509739583</t>
+          <t>-0.0027711255559356718 +/- 0.0015486103725974997</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-0.0006500171057132964 +/- 0.00035717777998323644</t>
+          <t>-6.842285323298558e-05 +/- 0.00025601487422334974</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0.007252822442695883 +/- 0.0010125657603112393</t>
+          <t>0.007629148135477259 +/- 0.001271358479374755</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.005029079712624007 +/- 0.0010931608148252137</t>
+          <t>-0.0060896339377351835 +/- 0.0010125657603112421</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>0.028498118371536117 +/- 0.004554233540677473</t>
+          <t>0.028600752651385564 +/- 0.004531432279110076</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>0.04673280875812521 +/- 0.002775978484447584</t>
+          <t>0.04755388299692097 +/- 0.0028003259568499684</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>0.07817310981867945 +/- 0.004458655936898017</t>
+          <t>0.07752309271296615 +/- 0.004215647430926953</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -7131,12 +7131,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>-0.013342456380431045 +/- 0.0043705013815042775</t>
+          <t>-0.013308244953814575 +/- 0.004040570807278194</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>-0.004618542593226105 +/- 0.006399000200349625</t>
+          <t>-0.005302771125555927 +/- 0.006450010831177748</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="DB9" t="inlineStr">
         <is>
-          <t>0.0018474170372904553 +/- 0.0024727076290923856</t>
+          <t>0.0019500513171399226 +/- 0.002560377316738624</t>
         </is>
       </c>
       <c r="DC9" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="DF9" t="inlineStr">
         <is>
-          <t>0.29469722887444405 +/- 0.0049155046337767535</t>
+          <t>0.2947314403010605 +/- 0.004939376536428353</t>
         </is>
       </c>
       <c r="DG9" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>0.02487170715018816 +/- 0.001683327348633944</t>
+          <t>0.025316455696202545 +/- 0.0018675804398160948</t>
         </is>
       </c>
       <c r="DL9" t="inlineStr">
@@ -7216,22 +7216,22 @@
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>-0.012555593568251788 +/- 0.003722762882800232</t>
+          <t>-0.012521382141635295 +/- 0.0037762968803411886</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
         <is>
-          <t>-0.016455696202531643 +/- 0.0022142485289475843</t>
+          <t>-0.016489907629148128 +/- 0.0022318859295655316</t>
         </is>
       </c>
       <c r="DQ9" t="inlineStr">
         <is>
-          <t>-0.0004447485460143619 +/- 0.00040623818292978466</t>
+          <t>-0.0003763256927813874 +/- 0.000357177779983246</t>
         </is>
       </c>
       <c r="DR9" t="inlineStr">
         <is>
-          <t>-0.0004447485460143619 +/- 0.00040623818292978466</t>
+          <t>-0.00047895997263085465 +/- 0.0003809623238337222</t>
         </is>
       </c>
       <c r="DS9" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>0.08600752651385565 +/- 0.00510014236156941</t>
+          <t>0.0858022579541567 +/- 0.0050507931670094024</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
         <is>
-          <t>0.03876154635648309 +/- 0.003338200879473969</t>
+          <t>0.03947998631542936 +/- 0.0030106055422511016</t>
         </is>
       </c>
       <c r="DV9" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="DX9" t="inlineStr">
         <is>
-          <t>-0.027129661306876475 +/- 0.003754070833612785</t>
+          <t>-0.02709544988025998 +/- 0.00375329131766061</t>
         </is>
       </c>
       <c r="DY9" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="EB9" t="inlineStr">
         <is>
-          <t>-0.012555593568251788 +/- 0.003722762882800232</t>
+          <t>-0.012555593568251778 +/- 0.003703851087208954</t>
         </is>
       </c>
       <c r="EC9" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="EJ9" t="inlineStr">
         <is>
-          <t>0.01652411905576464 +/- 0.0014026684912760857</t>
+          <t>0.016182004789599747 +/- 0.0013858795142339384</t>
         </is>
       </c>
       <c r="EK9" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="EQ9" t="inlineStr">
         <is>
-          <t>-0.030379746835443044 +/- 0.0020966888054799126</t>
+          <t>-0.030379746835443044 +/- 0.0020053850003083</t>
         </is>
       </c>
       <c r="ER9" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="ET9" t="inlineStr">
         <is>
-          <t>0.016216216216216238 +/- 0.0013529743368652116</t>
+          <t>0.01648990762914815 +/- 0.0013752823292673207</t>
         </is>
       </c>
       <c r="EU9" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.02687196110210698 +/- 0.0028900215430385616</t>
+          <t>-0.02690437601296597 +/- 0.002884744954461848</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-0.01277147487844409 +/- 0.0026020917005367366</t>
+          <t>-0.012739059967585098 +/- 0.0025771383092772875</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>-0.006774716369529987 +/- 0.0009664863219368173</t>
+          <t>-0.006807131280388979 +/- 0.0009505917859718011</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>-0.0046029173419773195 +/- 0.0009372338602788294</t>
+          <t>-0.004570502431118317 +/- 0.0009333017859894932</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-0.011636952998379246 +/- 0.00180158097006032</t>
+          <t>-0.011669367909238237 +/- 0.0017695097651807034</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00014496388833060023</t>
+          <t>-6.482982171798212e-05 +/- 0.00012965964343596424</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.014469867869803487 +/- 0.0026119680203612237</t>
+          <t>0.014437640992587885 +/- 0.0026173303904926874</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>-0.003416048984853315 +/- 0.0010804418056229513</t>
+          <t>-0.003383822107637713 +/- 0.0011641889699122458</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
